--- a/EA_LBO_Model.xlsx
+++ b/EA_LBO_Model.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="xl"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -17,11 +17,6 @@
     <sheet name="Sensitivity" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1641,7 +1636,7 @@
         <v>0.0725</v>
       </c>
       <c r="F37" s="11" t="n">
-        <f aca="false">IF(D37="Yes",0,0)+E37</f>
+        <f aca="false">E37</f>
         <v>0.0725</v>
       </c>
       <c r="G37" s="13" t="n">
@@ -1668,7 +1663,7 @@
         <v>0.0625</v>
       </c>
       <c r="F38" s="11" t="n">
-        <f aca="false">IF(D38="Yes",0,0)+E38</f>
+        <f aca="false">E38</f>
         <v>0.0625</v>
       </c>
       <c r="G38" s="13" t="n">
@@ -1695,7 +1690,7 @@
         <v>0.0875</v>
       </c>
       <c r="F39" s="11" t="n">
-        <f aca="false">IF(D39="Yes",0,0)+E39</f>
+        <f aca="false">E39</f>
         <v>0.0875</v>
       </c>
       <c r="G39" s="13" t="n">
